--- a/1.data/trans_matrix.xlsx
+++ b/1.data/trans_matrix.xlsx
@@ -1,6 +1,6 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
@@ -10,13 +10,13 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF67D8BA-836D-4FB0-9197-8B0FB31D7BE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
     <sheet name="tmat" sheetId="1" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="true"/>
   <pivotCaches>
     <pivotCache cacheId="0" r:id="rId3"/>
   </pivotCaches>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="1030" uniqueCount="42">
   <si>
     <t>e_y</t>
   </si>
@@ -168,12 +168,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -208,14 +208,14 @@
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyBorder="true"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="true"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1426,7 +1426,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1577,7 +1577,7 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -1601,9 +1601,9 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -1627,7 +1627,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -1662,7 +1662,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="false">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -1680,7 +1680,7 @@
             <a:satMod val="170000"/>
           </a:schemeClr>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill rotWithShape="true">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
@@ -1705,7 +1705,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="5400000" scaled="false"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
@@ -1741,18 +1741,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6BA8F53-9FB6-4957-A911-E604BDF4C636}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6BA8F53-9FB6-4957-A911-E604BDF4C636}">
   <dimension ref="A1:O11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="6" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="15" width="4.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16" bestFit="true" customWidth="true"/>
+    <col min="2" max="2" width="16.28515625" bestFit="true" customWidth="true"/>
+    <col min="3" max="6" width="7.5703125" bestFit="true" customWidth="true"/>
+    <col min="7" max="7" width="11.28515625" bestFit="true" customWidth="true"/>
+    <col min="11" max="15" width="4.5703125" bestFit="true" customWidth="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>26</v>
       </c>
@@ -1760,7 +1760,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="2" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>29</v>
       </c>
@@ -1768,7 +1768,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>41</v>
       </c>
@@ -1776,7 +1776,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>38</v>
       </c>
@@ -1799,7 +1799,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="6" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>1</v>
       </c>
@@ -1842,7 +1842,7 @@
         <v>0.7968652037617554</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="7" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>2</v>
       </c>
@@ -1885,7 +1885,7 @@
         <v>4.1796875</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="8" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>3</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>11.015625</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="9" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>4</v>
       </c>
@@ -1971,7 +1971,7 @@
         <v>25.247812499999998</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="10" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>5</v>
       </c>
@@ -2014,7 +2014,7 @@
         <v>58.579439252336442</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" r="11" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>39</v>
       </c>
@@ -2046,11 +2046,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H101"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2076,7 +2076,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2084,7 +2084,7 @@
         <v>2000</v>
       </c>
       <c r="C2" s="1">
-        <v>0.60532983245811456</v>
+        <v>0.48022330582645662</v>
       </c>
       <c r="D2" t="s">
         <v>4</v>
@@ -2102,7 +2102,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -2110,7 +2110,7 @@
         <v>2000</v>
       </c>
       <c r="C3" s="1">
-        <v>0.25317925000000002</v>
+        <v>0.326934</v>
       </c>
       <c r="D3" t="s">
         <v>4</v>
@@ -2128,7 +2128,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -2136,7 +2136,7 @@
         <v>2000</v>
       </c>
       <c r="C4" s="1">
-        <v>9.6634249999999991E-2</v>
+        <v>0.21928724999999999</v>
       </c>
       <c r="D4" t="s">
         <v>4</v>
@@ -2154,7 +2154,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -2162,7 +2162,7 @@
         <v>2000</v>
       </c>
       <c r="C5" s="1">
-        <v>3.5463500000000002E-2</v>
+        <v>0.13466475</v>
       </c>
       <c r="D5" t="s">
         <v>4</v>
@@ -2180,7 +2180,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -2188,7 +2188,7 @@
         <v>2000</v>
       </c>
       <c r="C6" s="1">
-        <v>9.5423644088977761E-3</v>
+        <v>0.064659835041239691</v>
       </c>
       <c r="D6" t="s">
         <v>4</v>
@@ -2206,7 +2206,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -2214,7 +2214,7 @@
         <v>2000</v>
       </c>
       <c r="C7" s="1">
-        <v>0.24421305326331583</v>
+        <v>0.21123580895223804</v>
       </c>
       <c r="D7" t="s">
         <v>4</v>
@@ -2232,7 +2232,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8">
       <c r="A8" s="1">
         <v>2</v>
       </c>
@@ -2240,7 +2240,7 @@
         <v>2000</v>
       </c>
       <c r="C8" s="1">
-        <v>0.35488324999999998</v>
+        <v>0.215581</v>
       </c>
       <c r="D8" t="s">
         <v>4</v>
@@ -2258,7 +2258,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9">
       <c r="A9" s="1">
         <v>3</v>
       </c>
@@ -2266,7 +2266,7 @@
         <v>2000</v>
       </c>
       <c r="C9" s="1">
-        <v>0.2456055</v>
+        <v>0.18915074999999998</v>
       </c>
       <c r="D9" t="s">
         <v>4</v>
@@ -2284,7 +2284,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10">
       <c r="A10" s="1">
         <v>4</v>
       </c>
@@ -2292,7 +2292,7 @@
         <v>2000</v>
       </c>
       <c r="C10" s="1">
-        <v>0.11760474999999999</v>
+        <v>0.14380950000000001</v>
       </c>
       <c r="D10" t="s">
         <v>4</v>
@@ -2310,7 +2310,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11">
       <c r="A11" s="1">
         <v>5</v>
       </c>
@@ -2318,7 +2318,7 @@
         <v>2000</v>
       </c>
       <c r="C11" s="1">
-        <v>3.7745313671582105E-2</v>
+        <v>0.081243689077730566</v>
       </c>
       <c r="D11" t="s">
         <v>4</v>
@@ -2336,7 +2336,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -2344,7 +2344,7 @@
         <v>2000</v>
       </c>
       <c r="C12" s="1">
-        <v>0.10176744186046512</v>
+        <v>0.19216679169792447</v>
       </c>
       <c r="D12" t="s">
         <v>4</v>
@@ -2362,7 +2362,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -2370,7 +2370,7 @@
         <v>2000</v>
       </c>
       <c r="C13" s="1">
-        <v>0.24119450000000001</v>
+        <v>0.25346049999999998</v>
       </c>
       <c r="D13" t="s">
         <v>4</v>
@@ -2388,7 +2388,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14">
       <c r="A14" s="1">
         <v>3</v>
       </c>
@@ -2396,7 +2396,7 @@
         <v>2000</v>
       </c>
       <c r="C14" s="1">
-        <v>0.32100625000000005</v>
+        <v>0.27813399999999999</v>
       </c>
       <c r="D14" t="s">
         <v>4</v>
@@ -2414,7 +2414,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15">
       <c r="A15" s="1">
         <v>4</v>
       </c>
@@ -2422,7 +2422,7 @@
         <v>2000</v>
       </c>
       <c r="C15" s="1">
-        <v>0.240148</v>
+        <v>0.26398149999999998</v>
       </c>
       <c r="D15" t="s">
         <v>4</v>
@@ -2440,7 +2440,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16">
       <c r="A16" s="1">
         <v>5</v>
       </c>
@@ -2448,7 +2448,7 @@
         <v>2000</v>
       </c>
       <c r="C16" s="1">
-        <v>9.5884778805298679E-2</v>
+        <v>0.18695426143464136</v>
       </c>
       <c r="D16" t="s">
         <v>4</v>
@@ -2466,7 +2466,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17">
       <c r="A17" s="1">
         <v>1</v>
       </c>
@@ -2474,7 +2474,7 @@
         <v>2000</v>
       </c>
       <c r="C17" s="1">
-        <v>3.9582645661415353E-2</v>
+        <v>0.079049012253063267</v>
       </c>
       <c r="D17" t="s">
         <v>4</v>
@@ -2492,7 +2492,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -2500,7 +2500,7 @@
         <v>2000</v>
       </c>
       <c r="C18" s="1">
-        <v>0.1177695</v>
+        <v>0.12858050000000002</v>
       </c>
       <c r="D18" t="s">
         <v>4</v>
@@ -2518,7 +2518,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19">
       <c r="A19" s="1">
         <v>3</v>
       </c>
@@ -2526,7 +2526,7 @@
         <v>2000</v>
       </c>
       <c r="C19" s="1">
-        <v>0.24572225</v>
+        <v>0.17665075</v>
       </c>
       <c r="D19" t="s">
         <v>4</v>
@@ -2544,7 +2544,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20">
       <c r="A20" s="1">
         <v>4</v>
       </c>
@@ -2552,7 +2552,7 @@
         <v>2000</v>
       </c>
       <c r="C20" s="1">
-        <v>0.35881000000000002</v>
+        <v>0.21419925000000001</v>
       </c>
       <c r="D20" t="s">
         <v>4</v>
@@ -2570,7 +2570,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21">
       <c r="A21" s="1">
         <v>5</v>
       </c>
@@ -2578,7 +2578,7 @@
         <v>2000</v>
       </c>
       <c r="C21" s="1">
-        <v>0.23806698325418646</v>
+        <v>0.20113721569607598</v>
       </c>
       <c r="D21" t="s">
         <v>4</v>
@@ -2596,7 +2596,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22">
       <c r="A22" s="1">
         <v>1</v>
       </c>
@@ -2604,7 +2604,7 @@
         <v>2000</v>
       </c>
       <c r="C22" s="1">
-        <v>9.1070267566891721E-3</v>
+        <v>0.037325081270317584</v>
       </c>
       <c r="D22" t="s">
         <v>4</v>
@@ -2622,7 +2622,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23">
       <c r="A23" s="1">
         <v>2</v>
       </c>
@@ -2630,7 +2630,7 @@
         <v>2000</v>
       </c>
       <c r="C23" s="1">
-        <v>3.2973500000000003E-2</v>
+        <v>0.075443999999999997</v>
       </c>
       <c r="D23" t="s">
         <v>4</v>
@@ -2648,7 +2648,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -2656,7 +2656,7 @@
         <v>2000</v>
       </c>
       <c r="C24" s="1">
-        <v>9.1031750000000008E-2</v>
+        <v>0.13677725000000002</v>
       </c>
       <c r="D24" t="s">
         <v>4</v>
@@ -2674,7 +2674,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25">
       <c r="A25" s="1">
         <v>4</v>
       </c>
@@ -2682,7 +2682,7 @@
         <v>2000</v>
       </c>
       <c r="C25" s="1">
-        <v>0.24797374999999999</v>
+        <v>0.24334500000000001</v>
       </c>
       <c r="D25" t="s">
         <v>4</v>
@@ -2700,7 +2700,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26">
       <c r="A26" s="1">
         <v>5</v>
       </c>
@@ -2708,7 +2708,7 @@
         <v>2000</v>
       </c>
       <c r="C26" s="1">
-        <v>0.61876055986003498</v>
+        <v>0.46600499875031243</v>
       </c>
       <c r="D26" t="s">
         <v>4</v>
@@ -2726,7 +2726,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27">
       <c r="A27" s="1">
         <v>1</v>
       </c>
@@ -2734,7 +2734,7 @@
         <v>2000</v>
       </c>
       <c r="C27" s="1">
-        <v>0.77463704630788477</v>
+        <v>0.48546433041301629</v>
       </c>
       <c r="D27" t="s">
         <v>4</v>
@@ -2752,7 +2752,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28">
       <c r="A28" s="1">
         <v>2</v>
       </c>
@@ -2760,7 +2760,7 @@
         <v>2000</v>
       </c>
       <c r="C28" s="1">
-        <v>0.20580000000000001</v>
+        <v>0.32757875000000003</v>
       </c>
       <c r="D28" t="s">
         <v>4</v>
@@ -2778,7 +2778,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -2786,7 +2786,7 @@
         <v>2000</v>
       </c>
       <c r="C29" s="1">
-        <v>1.9676249999999999E-2</v>
+        <v>0.21731125000000001</v>
       </c>
       <c r="D29" t="s">
         <v>4</v>
@@ -2804,7 +2804,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30">
       <c r="A30" s="1">
         <v>4</v>
       </c>
@@ -2812,7 +2812,7 @@
         <v>2000</v>
       </c>
       <c r="C30" s="1">
-        <v>8.3625000000000008E-4</v>
+        <v>0.132215</v>
       </c>
       <c r="D30" t="s">
         <v>4</v>
@@ -2830,7 +2830,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31">
       <c r="A31" s="1">
         <v>5</v>
       </c>
@@ -2838,7 +2838,7 @@
         <v>2000</v>
       </c>
       <c r="C31" s="1">
-        <v>1.8726591760299626E-5</v>
+        <v>0.06247940074906367</v>
       </c>
       <c r="D31" t="s">
         <v>4</v>
@@ -2856,7 +2856,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32">
       <c r="A32" s="1">
         <v>1</v>
       </c>
@@ -2864,7 +2864,7 @@
         <v>2000</v>
       </c>
       <c r="C32" s="1">
-        <v>0.20101376720901126</v>
+        <v>0.21224780976220275</v>
       </c>
       <c r="D32" t="s">
         <v>4</v>
@@ -2882,7 +2882,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33">
       <c r="A33" s="1">
         <v>2</v>
       </c>
@@ -2890,7 +2890,7 @@
         <v>2000</v>
       </c>
       <c r="C33" s="1">
-        <v>0.51345499999999999</v>
+        <v>0.21619624999999998</v>
       </c>
       <c r="D33" t="s">
         <v>4</v>
@@ -2908,7 +2908,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34">
       <c r="A34" s="1">
         <v>3</v>
       </c>
@@ -2916,7 +2916,7 @@
         <v>2000</v>
       </c>
       <c r="C34" s="1">
-        <v>0.24811249999999999</v>
+        <v>0.19002250000000001</v>
       </c>
       <c r="D34" t="s">
         <v>4</v>
@@ -2934,7 +2934,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -2942,7 +2942,7 @@
         <v>2000</v>
       </c>
       <c r="C35" s="1">
-        <v>3.6510000000000001E-2</v>
+        <v>0.14257624999999999</v>
       </c>
       <c r="D35" t="s">
         <v>4</v>
@@ -2960,7 +2960,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36">
       <c r="A36" s="1">
         <v>5</v>
       </c>
@@ -2968,7 +2968,7 @@
         <v>2000</v>
       </c>
       <c r="C36" s="1">
-        <v>1.1585518102372034E-3</v>
+        <v>0.07964669163545568</v>
       </c>
       <c r="D36" t="s">
         <v>4</v>
@@ -2986,7 +2986,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37">
       <c r="A37" s="1">
         <v>1</v>
       </c>
@@ -2994,7 +2994,7 @@
         <v>2000</v>
       </c>
       <c r="C37" s="1">
-        <v>2.3120150187734671E-2</v>
+        <v>0.19249186483103881</v>
       </c>
       <c r="D37" t="s">
         <v>4</v>
@@ -3012,7 +3012,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38">
       <c r="A38" s="1">
         <v>2</v>
       </c>
@@ -3020,7 +3020,7 @@
         <v>2000</v>
       </c>
       <c r="C38" s="1">
-        <v>0.24364249999999998</v>
+        <v>0.25583875</v>
       </c>
       <c r="D38" t="s">
         <v>4</v>
@@ -3038,7 +3038,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39">
       <c r="A39" s="1">
         <v>3</v>
       </c>
@@ -3046,7 +3046,7 @@
         <v>2000</v>
       </c>
       <c r="C39" s="1">
-        <v>0.46701875000000004</v>
+        <v>0.27920125000000001</v>
       </c>
       <c r="D39" t="s">
         <v>4</v>
@@ -3064,7 +3064,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40">
       <c r="A40" s="1">
         <v>4</v>
       </c>
@@ -3072,7 +3072,7 @@
         <v>2000</v>
       </c>
       <c r="C40" s="1">
-        <v>0.24452499999999999</v>
+        <v>0.26232375000000002</v>
       </c>
       <c r="D40" t="s">
         <v>4</v>
@@ -3090,7 +3090,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41">
       <c r="A41" s="1">
         <v>5</v>
       </c>
@@ -3098,7 +3098,7 @@
         <v>2000</v>
       </c>
       <c r="C41" s="1">
-        <v>2.169538077403246E-2</v>
+        <v>0.1807940074906367</v>
       </c>
       <c r="D41" t="s">
         <v>4</v>
@@ -3116,7 +3116,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42">
       <c r="A42" s="1">
         <v>1</v>
       </c>
@@ -3124,7 +3124,7 @@
         <v>2000</v>
       </c>
       <c r="C42" s="1">
-        <v>1.219023779724656E-3</v>
+        <v>0.077254067584480599</v>
       </c>
       <c r="D42" t="s">
         <v>4</v>
@@ -3142,7 +3142,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43">
       <c r="A43" s="1">
         <v>2</v>
       </c>
@@ -3150,7 +3150,7 @@
         <v>2000</v>
       </c>
       <c r="C43" s="1">
-        <v>3.6285000000000005E-2</v>
+        <v>0.12991</v>
       </c>
       <c r="D43" t="s">
         <v>4</v>
@@ -3168,7 +3168,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44">
       <c r="A44" s="1">
         <v>3</v>
       </c>
@@ -3176,7 +3176,7 @@
         <v>2000</v>
       </c>
       <c r="C44" s="1">
-        <v>0.24606375</v>
+        <v>0.18053374999999999</v>
       </c>
       <c r="D44" t="s">
         <v>4</v>
@@ -3194,7 +3194,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45">
       <c r="A45" s="1">
         <v>4</v>
       </c>
@@ -3202,7 +3202,7 @@
         <v>2000</v>
       </c>
       <c r="C45" s="1">
-        <v>0.51754750000000005</v>
+        <v>0.21884624999999999</v>
       </c>
       <c r="D45" t="s">
         <v>4</v>
@@ -3220,7 +3220,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -3228,7 +3228,7 @@
         <v>2000</v>
       </c>
       <c r="C46" s="1">
-        <v>0.19863795255930089</v>
+        <v>0.20088514357053683</v>
       </c>
       <c r="D46" t="s">
         <v>4</v>
@@ -3246,7 +3246,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47">
       <c r="A47" s="1">
         <v>1</v>
       </c>
@@ -3254,7 +3254,7 @@
         <v>2000</v>
       </c>
       <c r="C47" s="1">
-        <v>1.0012515644555695E-5</v>
+        <v>0.032541927409261574</v>
       </c>
       <c r="D47" t="s">
         <v>4</v>
@@ -3272,7 +3272,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48">
       <c r="A48" s="1">
         <v>2</v>
       </c>
@@ -3280,7 +3280,7 @@
         <v>2000</v>
       </c>
       <c r="C48" s="1">
-        <v>8.1749999999999998E-4</v>
+        <v>0.070476250000000004</v>
       </c>
       <c r="D48" t="s">
         <v>4</v>
@@ -3298,7 +3298,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49">
       <c r="A49" s="1">
         <v>3</v>
       </c>
@@ -3306,7 +3306,7 @@
         <v>2000</v>
       </c>
       <c r="C49" s="1">
-        <v>1.912875E-2</v>
+        <v>0.13293125</v>
       </c>
       <c r="D49" t="s">
         <v>4</v>
@@ -3324,7 +3324,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50">
       <c r="A50" s="1">
         <v>4</v>
       </c>
@@ -3332,7 +3332,7 @@
         <v>2000</v>
       </c>
       <c r="C50" s="1">
-        <v>0.20058125000000002</v>
+        <v>0.24403875</v>
       </c>
       <c r="D50" t="s">
         <v>4</v>
@@ -3350,7 +3350,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -3358,7 +3358,7 @@
         <v>2000</v>
       </c>
       <c r="C51" s="1">
-        <v>0.77848938826466918</v>
+        <v>0.4761947565543071</v>
       </c>
       <c r="D51" t="s">
         <v>4</v>
@@ -3376,7 +3376,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52">
       <c r="A52" s="1">
         <v>1</v>
       </c>
@@ -3384,7 +3384,7 @@
         <v>2000</v>
       </c>
       <c r="C52" s="1">
-        <v>0.58959239809952491</v>
+        <v>0.4796949237309327</v>
       </c>
       <c r="D52" t="s">
         <v>4</v>
@@ -3402,7 +3402,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53">
       <c r="A53" s="1">
         <v>2</v>
       </c>
@@ -3410,7 +3410,7 @@
         <v>2000</v>
       </c>
       <c r="C53" s="1">
-        <v>0.26076625000000003</v>
+        <v>0.32485275000000002</v>
       </c>
       <c r="D53" t="s">
         <v>4</v>
@@ -3428,7 +3428,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54">
       <c r="A54" s="1">
         <v>3</v>
       </c>
@@ -3436,7 +3436,7 @@
         <v>2000</v>
       </c>
       <c r="C54" s="1">
-        <v>0.10431225000000001</v>
+        <v>0.21647325000000001</v>
       </c>
       <c r="D54" t="s">
         <v>4</v>
@@ -3454,7 +3454,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55">
       <c r="A55" s="1">
         <v>4</v>
       </c>
@@ -3462,7 +3462,7 @@
         <v>2000</v>
       </c>
       <c r="C55" s="1">
-        <v>3.6279249999999999E-2</v>
+        <v>0.13190525</v>
       </c>
       <c r="D55" t="s">
         <v>4</v>
@@ -3480,7 +3480,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56">
       <c r="A56" s="1">
         <v>5</v>
       </c>
@@ -3488,7 +3488,7 @@
         <v>2000</v>
       </c>
       <c r="C56" s="1">
-        <v>9.1949512621844528E-3</v>
+        <v>0.062823294176455893</v>
       </c>
       <c r="D56" t="s">
         <v>4</v>
@@ -3506,7 +3506,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57">
       <c r="A57" s="1">
         <v>1</v>
       </c>
@@ -3514,7 +3514,7 @@
         <v>2000</v>
       </c>
       <c r="C57" s="1">
-        <v>0.25175643910977741</v>
+        <v>0.20866816704176042</v>
       </c>
       <c r="D57" t="s">
         <v>4</v>
@@ -3532,7 +3532,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58">
       <c r="A58" s="1">
         <v>2</v>
       </c>
@@ -3540,7 +3540,7 @@
         <v>2000</v>
       </c>
       <c r="C58" s="1">
-        <v>0.33476149999999999</v>
+        <v>0.21254425000000002</v>
       </c>
       <c r="D58" t="s">
         <v>4</v>
@@ -3558,7 +3558,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59">
       <c r="A59" s="1">
         <v>3</v>
       </c>
@@ -3566,7 +3566,7 @@
         <v>2000</v>
       </c>
       <c r="C59" s="1">
-        <v>0.24766099999999999</v>
+        <v>0.18576124999999999</v>
       </c>
       <c r="D59" t="s">
         <v>4</v>
@@ -3584,7 +3584,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60">
       <c r="A60" s="1">
         <v>4</v>
       </c>
@@ -3592,7 +3592,7 @@
         <v>2000</v>
       </c>
       <c r="C60" s="1">
-        <v>0.12685250000000001</v>
+        <v>0.14029575</v>
       </c>
       <c r="D60" t="s">
         <v>4</v>
@@ -3610,7 +3610,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61">
       <c r="A61" s="1">
         <v>5</v>
       </c>
@@ -3618,7 +3618,7 @@
         <v>2000</v>
       </c>
       <c r="C61" s="1">
-        <v>3.9022494376405897E-2</v>
+        <v>0.078449137715571118</v>
       </c>
       <c r="D61" t="s">
         <v>4</v>
@@ -3636,7 +3636,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62">
       <c r="A62" s="1">
         <v>1</v>
       </c>
@@ -3644,7 +3644,7 @@
         <v>2000</v>
       </c>
       <c r="C62" s="1">
-        <v>0.10909102275568892</v>
+        <v>0.20737834458614654</v>
       </c>
       <c r="D62" t="s">
         <v>4</v>
@@ -3662,7 +3662,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63">
       <c r="A63" s="1">
         <v>2</v>
       </c>
@@ -3670,7 +3670,7 @@
         <v>2000</v>
       </c>
       <c r="C63" s="1">
-        <v>0.24388675000000001</v>
+        <v>0.275648</v>
       </c>
       <c r="D63" t="s">
         <v>4</v>
@@ -3688,7 +3688,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64">
       <c r="A64" s="1">
         <v>3</v>
       </c>
@@ -3696,7 +3696,7 @@
         <v>2000</v>
       </c>
       <c r="C64" s="1">
-        <v>0.30160175</v>
+        <v>0.30366375000000001</v>
       </c>
       <c r="D64" t="s">
         <v>4</v>
@@ -3714,7 +3714,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65">
       <c r="A65" s="1">
         <v>4</v>
       </c>
@@ -3722,7 +3722,7 @@
         <v>2000</v>
       </c>
       <c r="C65" s="1">
-        <v>0.24270874999999997</v>
+        <v>0.28903325000000002</v>
       </c>
       <c r="D65" t="s">
         <v>4</v>
@@ -3740,7 +3740,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66">
       <c r="A66" s="1">
         <v>5</v>
       </c>
@@ -3748,7 +3748,7 @@
         <v>2000</v>
       </c>
       <c r="C66" s="1">
-        <v>0.10271282179455136</v>
+        <v>0.204329167708073</v>
       </c>
       <c r="D66" t="s">
         <v>4</v>
@@ -3766,7 +3766,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67">
       <c r="A67" s="1">
         <v>1</v>
       </c>
@@ -3774,7 +3774,7 @@
         <v>2000</v>
       </c>
       <c r="C67" s="1">
-        <v>4.0844961240310076E-2</v>
+        <v>0.067815453863465866</v>
       </c>
       <c r="D67" t="s">
         <v>4</v>
@@ -3792,7 +3792,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68">
       <c r="A68" s="1">
         <v>2</v>
       </c>
@@ -3800,7 +3800,7 @@
         <v>2000</v>
       </c>
       <c r="C68" s="1">
-        <v>0.1272045</v>
+        <v>0.11249575000000001</v>
       </c>
       <c r="D68" t="s">
         <v>4</v>
@@ -3818,7 +3818,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69">
       <c r="A69" s="1">
         <v>3</v>
       </c>
@@ -3826,7 +3826,7 @@
         <v>2000</v>
       </c>
       <c r="C69" s="1">
-        <v>0.248528</v>
+        <v>0.15727025</v>
       </c>
       <c r="D69" t="s">
         <v>4</v>
@@ -3844,7 +3844,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70">
       <c r="A70" s="1">
         <v>4</v>
       </c>
@@ -3852,7 +3852,7 @@
         <v>2000</v>
       </c>
       <c r="C70" s="1">
-        <v>0.33868025000000002</v>
+        <v>0.19279374999999999</v>
       </c>
       <c r="D70" t="s">
         <v>4</v>
@@ -3870,7 +3870,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71">
       <c r="A71" s="1">
         <v>5</v>
       </c>
@@ -3878,7 +3878,7 @@
         <v>2000</v>
       </c>
       <c r="C71" s="1">
-        <v>0.24469107723069231</v>
+        <v>0.18130117470632343</v>
       </c>
       <c r="D71" t="s">
         <v>4</v>
@@ -3896,7 +3896,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72">
       <c r="A72" s="1">
         <v>1</v>
       </c>
@@ -3904,7 +3904,7 @@
         <v>2000</v>
       </c>
       <c r="C72" s="1">
-        <v>8.7151787946986754E-3</v>
+        <v>0.036443110777694424</v>
       </c>
       <c r="D72" t="s">
         <v>4</v>
@@ -3922,7 +3922,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73">
       <c r="A73" s="1">
         <v>2</v>
       </c>
@@ -3930,7 +3930,7 @@
         <v>2000</v>
       </c>
       <c r="C73" s="1">
-        <v>3.3381000000000001E-2</v>
+        <v>0.074459249999999991</v>
       </c>
       <c r="D73" t="s">
         <v>4</v>
@@ -3948,7 +3948,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74">
       <c r="A74" s="1">
         <v>3</v>
       </c>
@@ -3956,7 +3956,7 @@
         <v>2000</v>
       </c>
       <c r="C74" s="1">
-        <v>9.7897000000000012E-2</v>
+        <v>0.1368315</v>
       </c>
       <c r="D74" t="s">
         <v>4</v>
@@ -3974,7 +3974,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75">
       <c r="A75" s="1">
         <v>4</v>
       </c>
@@ -3982,7 +3982,7 @@
         <v>2000</v>
       </c>
       <c r="C75" s="1">
-        <v>0.25547924999999999</v>
+        <v>0.245972</v>
       </c>
       <c r="D75" t="s">
         <v>4</v>
@@ -4000,7 +4000,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76">
       <c r="A76" s="1">
         <v>5</v>
       </c>
@@ -4008,7 +4008,7 @@
         <v>2000</v>
       </c>
       <c r="C76" s="1">
-        <v>0.60437865533616597</v>
+        <v>0.4730972256935766</v>
       </c>
       <c r="D76" t="s">
         <v>4</v>
@@ -4026,7 +4026,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77">
       <c r="A77" s="1">
         <v>1</v>
       </c>
@@ -4034,7 +4034,7 @@
         <v>2000</v>
       </c>
       <c r="C77" s="1">
-        <v>0.59025907384230292</v>
+        <v>0.47994868585732165</v>
       </c>
       <c r="D77" t="s">
         <v>4</v>
@@ -4052,7 +4052,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78">
       <c r="A78" s="1">
         <v>2</v>
       </c>
@@ -4060,7 +4060,7 @@
         <v>2000</v>
       </c>
       <c r="C78" s="1">
-        <v>0.26136624999999997</v>
+        <v>0.32489375000000004</v>
       </c>
       <c r="D78" t="s">
         <v>4</v>
@@ -4078,7 +4078,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79">
       <c r="A79" s="1">
         <v>3</v>
       </c>
@@ -4086,7 +4086,7 @@
         <v>2000</v>
       </c>
       <c r="C79" s="1">
-        <v>0.10369375</v>
+        <v>0.21602375000000001</v>
       </c>
       <c r="D79" t="s">
         <v>4</v>
@@ -4104,7 +4104,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80">
       <c r="A80" s="1">
         <v>4</v>
       </c>
@@ -4112,7 +4112,7 @@
         <v>2000</v>
       </c>
       <c r="C80" s="1">
-        <v>3.6212500000000002E-2</v>
+        <v>0.13201500000000002</v>
       </c>
       <c r="D80" t="s">
         <v>4</v>
@@ -4130,7 +4130,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81">
       <c r="A81" s="1">
         <v>5</v>
       </c>
@@ -4138,7 +4138,7 @@
         <v>2000</v>
       </c>
       <c r="C81" s="1">
-        <v>9.1960049937578042E-3</v>
+        <v>0.063004993757802746</v>
       </c>
       <c r="D81" t="s">
         <v>4</v>
@@ -4156,7 +4156,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82">
       <c r="A82" s="1">
         <v>1</v>
       </c>
@@ -4164,7 +4164,7 @@
         <v>2000</v>
       </c>
       <c r="C82" s="1">
-        <v>0.25148685857321651</v>
+        <v>0.20927033792240299</v>
       </c>
       <c r="D82" t="s">
         <v>4</v>
@@ -4182,7 +4182,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83">
       <c r="A83" s="1">
         <v>2</v>
       </c>
@@ -4190,7 +4190,7 @@
         <v>2000</v>
       </c>
       <c r="C83" s="1">
-        <v>0.33534249999999999</v>
+        <v>0.21247875</v>
       </c>
       <c r="D83" t="s">
         <v>4</v>
@@ -4208,7 +4208,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84">
       <c r="A84" s="1">
         <v>3</v>
       </c>
@@ -4216,7 +4216,7 @@
         <v>2000</v>
       </c>
       <c r="C84" s="1">
-        <v>0.24818124999999999</v>
+        <v>0.18678999999999998</v>
       </c>
       <c r="D84" t="s">
         <v>4</v>
@@ -4234,7 +4234,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85">
       <c r="A85" s="1">
         <v>4</v>
       </c>
@@ -4242,7 +4242,7 @@
         <v>2000</v>
       </c>
       <c r="C85" s="1">
-        <v>0.12632125</v>
+        <v>0.140185</v>
       </c>
       <c r="D85" t="s">
         <v>4</v>
@@ -4260,7 +4260,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86">
       <c r="A86" s="1">
         <v>5</v>
       </c>
@@ -4268,7 +4268,7 @@
         <v>2000</v>
       </c>
       <c r="C86" s="1">
-        <v>3.8932584269662916E-2</v>
+        <v>0.079036204744069902</v>
       </c>
       <c r="D86" t="s">
         <v>4</v>
@@ -4286,7 +4286,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87">
       <c r="A87" s="1">
         <v>1</v>
       </c>
@@ -4294,7 +4294,7 @@
         <v>2000</v>
       </c>
       <c r="C87" s="1">
-        <v>0.10861576971214018</v>
+        <v>0.20328035043804754</v>
       </c>
       <c r="D87" t="s">
         <v>4</v>
@@ -4312,7 +4312,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88">
       <c r="A88" s="1">
         <v>2</v>
       </c>
@@ -4320,7 +4320,7 @@
         <v>2000</v>
       </c>
       <c r="C88" s="1">
-        <v>0.24407124999999999</v>
+        <v>0.27031124999999995</v>
       </c>
       <c r="D88" t="s">
         <v>4</v>
@@ -4338,7 +4338,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89">
       <c r="A89" s="1">
         <v>3</v>
       </c>
@@ -4346,7 +4346,7 @@
         <v>2000</v>
       </c>
       <c r="C89" s="1">
-        <v>0.30167749999999999</v>
+        <v>0.29611750000000003</v>
       </c>
       <c r="D89" t="s">
         <v>4</v>
@@ -4364,7 +4364,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90">
       <c r="A90" s="1">
         <v>4</v>
       </c>
@@ -4372,7 +4372,7 @@
         <v>2000</v>
       </c>
       <c r="C90" s="1">
-        <v>0.24309749999999999</v>
+        <v>0.28076249999999997</v>
       </c>
       <c r="D90" t="s">
         <v>4</v>
@@ -4390,7 +4390,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91">
       <c r="A91" s="1">
         <v>5</v>
       </c>
@@ -4398,7 +4398,7 @@
         <v>2000</v>
       </c>
       <c r="C91" s="1">
-        <v>0.10254556803995007</v>
+        <v>0.19736579275905117</v>
       </c>
       <c r="D91" t="s">
         <v>4</v>
@@ -4416,7 +4416,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92">
       <c r="A92" s="1">
         <v>1</v>
       </c>
@@ -4424,7 +4424,7 @@
         <v>2000</v>
       </c>
       <c r="C92" s="1">
-        <v>4.1028785982478097E-2</v>
+        <v>0.071030037546933669</v>
       </c>
       <c r="D92" t="s">
         <v>4</v>
@@ -4442,7 +4442,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93">
       <c r="A93" s="1">
         <v>2</v>
       </c>
@@ -4450,7 +4450,7 @@
         <v>2000</v>
       </c>
       <c r="C93" s="1">
-        <v>0.12622749999999999</v>
+        <v>0.11702875</v>
       </c>
       <c r="D93" t="s">
         <v>4</v>
@@ -4468,7 +4468,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94">
       <c r="A94" s="1">
         <v>3</v>
       </c>
@@ -4476,7 +4476,7 @@
         <v>2000</v>
       </c>
       <c r="C94" s="1">
-        <v>0.24884875000000001</v>
+        <v>0.16333</v>
       </c>
       <c r="D94" t="s">
         <v>4</v>
@@ -4494,7 +4494,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95">
       <c r="A95" s="1">
         <v>4</v>
       </c>
@@ -4502,7 +4502,7 @@
         <v>2000</v>
       </c>
       <c r="C95" s="1">
-        <v>0.33944875000000002</v>
+        <v>0.19951374999999999</v>
       </c>
       <c r="D95" t="s">
         <v>4</v>
@@ -4520,7 +4520,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96">
       <c r="A96" s="1">
         <v>5</v>
       </c>
@@ -4528,7 +4528,7 @@
         <v>2000</v>
       </c>
       <c r="C96" s="1">
-        <v>0.24419225967540575</v>
+        <v>0.18629962546816481</v>
       </c>
       <c r="D96" t="s">
         <v>4</v>
@@ -4546,7 +4546,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97">
       <c r="A97" s="1">
         <v>1</v>
       </c>
@@ -4554,7 +4554,7 @@
         <v>2000</v>
       </c>
       <c r="C97" s="1">
-        <v>8.6095118898623264E-3</v>
+        <v>0.036470588235294116</v>
       </c>
       <c r="D97" t="s">
         <v>4</v>
@@ -4572,7 +4572,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98">
       <c r="A98" s="1">
         <v>2</v>
       </c>
@@ -4580,7 +4580,7 @@
         <v>2000</v>
       </c>
       <c r="C98" s="1">
-        <v>3.2992500000000001E-2</v>
+        <v>0.075287499999999993</v>
       </c>
       <c r="D98" t="s">
         <v>4</v>
@@ -4598,7 +4598,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99">
       <c r="A99" s="1">
         <v>3</v>
       </c>
@@ -4606,7 +4606,7 @@
         <v>2000</v>
       </c>
       <c r="C99" s="1">
-        <v>9.7598749999999998E-2</v>
+        <v>0.13773875000000002</v>
       </c>
       <c r="D99" t="s">
         <v>4</v>
@@ -4624,7 +4624,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100">
       <c r="A100" s="1">
         <v>4</v>
       </c>
@@ -4632,7 +4632,7 @@
         <v>2000</v>
       </c>
       <c r="C100" s="1">
-        <v>0.25491999999999998</v>
+        <v>0.24752375000000001</v>
       </c>
       <c r="D100" t="s">
         <v>4</v>
@@ -4650,7 +4650,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101">
       <c r="A101" s="1">
         <v>5</v>
       </c>
@@ -4658,7 +4658,7 @@
         <v>2000</v>
       </c>
       <c r="C101" s="1">
-        <v>0.60513358302122344</v>
+        <v>0.47429338327091136</v>
       </c>
       <c r="D101" t="s">
         <v>4</v>
